--- a/outputs/CONSOLIDATED_all_measurements.xlsx
+++ b/outputs/CONSOLIDATED_all_measurements.xlsx
@@ -5148,7 +5148,7 @@
         <v>6.188679245283019</v>
       </c>
       <c r="D2" t="n">
-        <v>3.66404885219776</v>
+        <v>3.664048852197761</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -5396,7 +5396,7 @@
         <v>1.449547169811321</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2786108787730338</v>
+        <v>0.2786108787730339</v>
       </c>
       <c r="E10" t="n">
         <v>1.063</v>
@@ -5551,7 +5551,7 @@
         <v>249.9622641509434</v>
       </c>
       <c r="D15" t="n">
-        <v>13.71826724894575</v>
+        <v>13.71826724894576</v>
       </c>
       <c r="E15" t="n">
         <v>195</v>
@@ -5644,7 +5644,7 @@
         <v>-0.02324528301886792</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9216973661853936</v>
+        <v>0.9216973661853934</v>
       </c>
       <c r="E18" t="n">
         <v>-1.488</v>
@@ -5861,7 +5861,7 @@
         <v>177.0309245283018</v>
       </c>
       <c r="D25" t="n">
-        <v>39.23522753293908</v>
+        <v>39.23522753293911</v>
       </c>
       <c r="E25" t="n">
         <v>131.956</v>
